--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260629.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,306,027</t>
+          <t>42,376,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>63.95%</t>
+          <t>64.09%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,554,703</t>
+          <t>2,558,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.38%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,189,000</t>
+          <t>21,224,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,757,267</t>
+          <t>5,767,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,241,286</t>
+          <t>20,275,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,732,608</t>
+          <t>2,737,608</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>497,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,288,901</t>
+          <t>2,292,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,586,285</t>
+          <t>4,594,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>555,222</t>
+          <t>556,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5,368,296</t>
+          <t>5,377,296</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,979,288</t>
+          <t>1,983,288</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,39 +887,39 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,171,617</t>
+          <t>12,758,134</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12,737,134</t>
+          <t>180,515</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,44 +931,44 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,239,520</t>
+          <t>1,172,617</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>5,248,520</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -985,51 +985,51 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,323,000</t>
+          <t>1,325,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>596,600</t>
+          <t>3,400,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>3,394,000</t>
+          <t>597,600</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>849,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,22 +1085,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>847,349</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1122,46 +1122,46 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,887,321</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>1,890,321</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>151,499</t>
+          <t>992,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,44 +1217,44 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>990,822</t>
+          <t>3,193,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,187,000</t>
+          <t>151,499</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>571,000</t>
+          <t>572,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,659,000</t>
+          <t>5,668,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,39 +1305,39 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>372,000</t>
+          <t>1,816,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,813,000</t>
+          <t>372,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,39 +1349,39 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>761,000</t>
+          <t>1,185,441</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,183,441</t>
+          <t>762,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>799,897</t>
+          <t>800,897</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1447,73 +1447,73 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>576,000</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>10,503,121</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,364,384</t>
+          <t>144,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,485,121</t>
+          <t>928,659</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,39 +1525,39 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>926,659</t>
+          <t>4,412,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,405,578</t>
+          <t>1,366,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,442,981</t>
+          <t>3,448,981</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,51 +1601,51 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,568,703</t>
+          <t>2,573,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>492,000</t>
+          <t>7,103,249</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,091,249</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,166,107</t>
+          <t>2,170,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,39 +1701,39 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>769,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>768,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>796,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,906,956</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,172,076</t>
+          <t>4,914,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>1,174,076</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,39 +1833,39 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>385,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>287,000</t>
+          <t>1,545,400</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,543,400</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>316,000</t>
+          <t>317,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,39 +1943,39 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>992,121</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>994,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,739,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>251,000</t>
+          <t>252,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>674,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>672,000</t>
+          <t>333,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>766,238,977</t>
+          <t>964,574,283</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -2235,10 +2235,28 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>389,636,442</t>
+          <t>411,714,042</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-565,252,385</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
